--- a/Accrediation.xlsx
+++ b/Accrediation.xlsx
@@ -1178,7 +1178,7 @@
     <t>مدرب - مراجع</t>
   </si>
   <si>
-    <t xml:space="preserve"> الاعتماد</t>
+    <t>فئة الاعتماد</t>
   </si>
 </sst>
 </file>
@@ -1204,19 +1204,19 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="178"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="178"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="178"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1375,9 +1375,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1394,91 +1391,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1760,9 +1689,9 @@
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.25" customWidth="1"/>
-    <col min="4" max="4" width="26.5" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5" style="26" customWidth="1"/>
-    <col min="6" max="6" width="20.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="23" customWidth="1"/>
+    <col min="6" max="6" width="20.875" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1775,13 +1704,13 @@
       <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>383</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1798,11 +1727,11 @@
       <c r="C2" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>98</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -1819,11 +1748,11 @@
       <c r="C3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="23"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="19" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1840,13 +1769,13 @@
       <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -1863,9 +1792,9 @@
       <c r="C5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="23"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="20">
+      <c r="F5" s="19">
         <v>27610130100231</v>
       </c>
       <c r="G5" s="10"/>
@@ -1880,11 +1809,11 @@
       <c r="C6" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D6" s="23"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>310</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1901,13 +1830,13 @@
       <c r="C7" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>155</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -1924,9 +1853,9 @@
       <c r="C8" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D8" s="23"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <v>27008212100334</v>
       </c>
       <c r="G8" s="10"/>
@@ -1941,11 +1870,11 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="23"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1962,11 +1891,11 @@
       <c r="C10" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D10" s="23"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>298</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1983,11 +1912,11 @@
       <c r="C11" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>257</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -2004,11 +1933,11 @@
       <c r="C12" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="20">
+      <c r="F12" s="19">
         <v>28308232100443</v>
       </c>
       <c r="G12" s="10"/>
@@ -2023,11 +1952,11 @@
       <c r="C13" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="23"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>210</v>
       </c>
       <c r="G13" s="7" t="s">
@@ -2044,11 +1973,11 @@
       <c r="C14" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="23"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G14" s="5" t="s">
@@ -2065,11 +1994,11 @@
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="23"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>7</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -2086,11 +2015,11 @@
       <c r="C16" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="23"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>279</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -2107,11 +2036,11 @@
       <c r="C17" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <v>28211012100961</v>
       </c>
       <c r="G17" s="10"/>
@@ -2126,11 +2055,11 @@
       <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="23"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="19" t="s">
         <v>41</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -2147,11 +2076,11 @@
       <c r="C19" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D19" s="23"/>
+      <c r="D19" s="22"/>
       <c r="E19" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="19" t="s">
         <v>302</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -2168,11 +2097,11 @@
       <c r="C20" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="20">
+      <c r="F20" s="19">
         <v>27905282101623</v>
       </c>
       <c r="G20" s="10"/>
@@ -2185,11 +2114,11 @@
       <c r="C21" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="22" t="s">
         <v>381</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>28311121700868</v>
       </c>
       <c r="G21" s="10"/>
@@ -2204,11 +2133,11 @@
       <c r="C22" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="23"/>
+      <c r="D22" s="22"/>
       <c r="E22" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19" t="s">
         <v>254</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -2225,11 +2154,11 @@
       <c r="C23" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="20">
+      <c r="F23" s="19">
         <v>26911111600105</v>
       </c>
       <c r="G23" s="10"/>
@@ -2244,11 +2173,11 @@
       <c r="C24" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D24" s="23"/>
+      <c r="D24" s="22"/>
       <c r="E24" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>261</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -2265,11 +2194,11 @@
       <c r="C25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D25" s="23"/>
+      <c r="D25" s="22"/>
       <c r="E25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>138</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -2286,11 +2215,11 @@
       <c r="C26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="23"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -2305,11 +2234,11 @@
       <c r="C27" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="22" t="s">
         <v>381</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="20">
+      <c r="F27" s="19">
         <v>28602242400173</v>
       </c>
       <c r="G27" s="10"/>
@@ -2324,11 +2253,11 @@
       <c r="C28" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="23"/>
+      <c r="D28" s="22"/>
       <c r="E28" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>95</v>
       </c>
       <c r="G28" s="5" t="s">
@@ -2345,11 +2274,11 @@
       <c r="C29" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="23"/>
+      <c r="D29" s="22"/>
       <c r="E29" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="19" t="s">
         <v>152</v>
       </c>
       <c r="G29" s="7" t="s">
@@ -2366,11 +2295,11 @@
       <c r="C30" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <v>27610010100415</v>
       </c>
       <c r="G30" s="10"/>
@@ -2385,11 +2314,11 @@
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="23"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -2406,11 +2335,11 @@
       <c r="C32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="20">
+      <c r="F32" s="19">
         <v>29106102102985</v>
       </c>
       <c r="G32" s="10"/>
@@ -2425,11 +2354,11 @@
       <c r="C33" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D33" s="23"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="19" t="s">
         <v>282</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -2446,11 +2375,11 @@
       <c r="C34" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D34" s="23"/>
+      <c r="D34" s="22"/>
       <c r="E34" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="19" t="s">
         <v>335</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -2467,11 +2396,11 @@
       <c r="C35" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D35" s="23"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="19" t="s">
         <v>163</v>
       </c>
       <c r="G35" s="7" t="s">
@@ -2488,11 +2417,11 @@
       <c r="C36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="23"/>
+      <c r="D36" s="22"/>
       <c r="E36" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="19" t="s">
         <v>85</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -2509,11 +2438,11 @@
       <c r="C37" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D37" s="23"/>
+      <c r="D37" s="22"/>
       <c r="E37" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="19" t="s">
         <v>229</v>
       </c>
       <c r="G37" s="7" t="s">
@@ -2530,11 +2459,11 @@
       <c r="C38" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="23"/>
+      <c r="D38" s="22"/>
       <c r="E38" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="19" t="s">
         <v>159</v>
       </c>
       <c r="G38" s="7" t="s">
@@ -2551,11 +2480,11 @@
       <c r="C39" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="20">
+      <c r="F39" s="19">
         <v>27201012105379</v>
       </c>
       <c r="G39" s="10"/>
@@ -2570,11 +2499,11 @@
       <c r="C40" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D40" s="23"/>
+      <c r="D40" s="22"/>
       <c r="E40" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="19" t="s">
         <v>306</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -2591,11 +2520,11 @@
       <c r="C41" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="23"/>
+      <c r="D41" s="22"/>
       <c r="E41" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="19" t="s">
         <v>104</v>
       </c>
       <c r="G41" s="5" t="s">
@@ -2612,11 +2541,11 @@
       <c r="C42" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D42" s="23"/>
+      <c r="D42" s="22"/>
       <c r="E42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="19" t="s">
         <v>62</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -2631,11 +2560,11 @@
       <c r="C43" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="22" t="s">
         <v>381</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="20">
+      <c r="F43" s="19">
         <v>26807292102274</v>
       </c>
       <c r="G43" s="10"/>
@@ -2650,11 +2579,11 @@
       <c r="C44" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="23"/>
+      <c r="D44" s="22"/>
       <c r="E44" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="19" t="s">
         <v>107</v>
       </c>
       <c r="G44" s="5" t="s">
@@ -2671,11 +2600,11 @@
       <c r="C45" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D45" s="23"/>
+      <c r="D45" s="22"/>
       <c r="E45" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="19" t="s">
         <v>225</v>
       </c>
       <c r="G45" s="7" t="s">
@@ -2692,11 +2621,11 @@
       <c r="C46" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D46" s="23"/>
+      <c r="D46" s="22"/>
       <c r="E46" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="19" t="s">
         <v>29</v>
       </c>
       <c r="G46" s="2" t="s">
@@ -2713,11 +2642,11 @@
       <c r="C47" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="23"/>
+      <c r="D47" s="22"/>
       <c r="E47" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="19" t="s">
         <v>110</v>
       </c>
       <c r="G47" s="5" t="s">
@@ -2734,11 +2663,11 @@
       <c r="C48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="23"/>
+      <c r="D48" s="22"/>
       <c r="E48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="19" t="s">
         <v>44</v>
       </c>
       <c r="G48" s="2" t="s">
@@ -2755,11 +2684,11 @@
       <c r="C49" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D49" s="23"/>
+      <c r="D49" s="22"/>
       <c r="E49" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="19" t="s">
         <v>338</v>
       </c>
       <c r="G49" s="2" t="s">
@@ -2776,11 +2705,11 @@
       <c r="C50" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <v>28407072104542</v>
       </c>
       <c r="G50" s="10"/>
@@ -2795,11 +2724,11 @@
       <c r="C51" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="23"/>
+      <c r="D51" s="22"/>
       <c r="E51" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="19" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
@@ -2816,11 +2745,11 @@
       <c r="C52" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D52" s="23"/>
+      <c r="D52" s="22"/>
       <c r="E52" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="19" t="s">
         <v>264</v>
       </c>
       <c r="G52" s="2" t="s">
@@ -2837,11 +2766,11 @@
       <c r="C53" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D53" s="23"/>
+      <c r="D53" s="22"/>
       <c r="E53" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="19" t="s">
         <v>267</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -2858,11 +2787,11 @@
       <c r="C54" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D54" s="23"/>
+      <c r="D54" s="22"/>
       <c r="E54" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="19" t="s">
         <v>313</v>
       </c>
       <c r="G54" s="2" t="s">
@@ -2879,11 +2808,11 @@
       <c r="C55" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D55" s="23"/>
+      <c r="D55" s="22"/>
       <c r="E55" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="F55" s="19" t="s">
         <v>342</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -2900,11 +2829,11 @@
       <c r="C56" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D56" s="23"/>
+      <c r="D56" s="22"/>
       <c r="E56" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" s="19" t="s">
         <v>233</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -2921,11 +2850,11 @@
       <c r="C57" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="23"/>
+      <c r="D57" s="22"/>
       <c r="E57" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="19" t="s">
         <v>113</v>
       </c>
       <c r="G57" s="5" t="s">
@@ -2942,11 +2871,11 @@
       <c r="C58" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D58" s="23"/>
+      <c r="D58" s="22"/>
       <c r="E58" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="19" t="s">
         <v>345</v>
       </c>
       <c r="G58" s="2" t="s">
@@ -2963,11 +2892,11 @@
       <c r="C59" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E59" s="5"/>
-      <c r="F59" s="20">
+      <c r="F59" s="19">
         <v>28602162103178</v>
       </c>
       <c r="G59" s="10"/>
@@ -2982,11 +2911,11 @@
       <c r="C60" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D60" s="23"/>
+      <c r="D60" s="22"/>
       <c r="E60" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" s="19" t="s">
         <v>214</v>
       </c>
       <c r="G60" s="7" t="s">
@@ -3003,11 +2932,11 @@
       <c r="C61" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D61" s="23"/>
+      <c r="D61" s="22"/>
       <c r="E61" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G61" s="2" t="s">
@@ -3024,11 +2953,11 @@
       <c r="C62" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="20">
+      <c r="F62" s="19">
         <v>27004071201161</v>
       </c>
       <c r="G62" s="10"/>
@@ -3043,11 +2972,11 @@
       <c r="C63" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D63" s="23"/>
+      <c r="D63" s="22"/>
       <c r="E63" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="F63" s="19" t="s">
         <v>348</v>
       </c>
       <c r="G63" s="2" t="s">
@@ -3064,11 +2993,11 @@
       <c r="C64" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D64" s="23"/>
+      <c r="D64" s="22"/>
       <c r="E64" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" s="19" t="s">
         <v>285</v>
       </c>
       <c r="G64" s="2" t="s">
@@ -3085,11 +3014,11 @@
       <c r="C65" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D65" s="23"/>
+      <c r="D65" s="22"/>
       <c r="E65" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F65" s="20" t="s">
+      <c r="F65" s="19" t="s">
         <v>116</v>
       </c>
       <c r="G65" s="5" t="s">
@@ -3106,11 +3035,11 @@
       <c r="C66" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D66" s="23"/>
+      <c r="D66" s="22"/>
       <c r="E66" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="20" t="s">
+      <c r="F66" s="19" t="s">
         <v>166</v>
       </c>
       <c r="G66" s="7" t="s">
@@ -3127,11 +3056,11 @@
       <c r="C67" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D67" s="23" t="s">
+      <c r="D67" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E67" s="5"/>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <v>28208242100439</v>
       </c>
       <c r="G67" s="10"/>
@@ -3146,11 +3075,11 @@
       <c r="C68" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D68" s="23"/>
+      <c r="D68" s="22"/>
       <c r="E68" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G68" s="2" t="s">
@@ -3167,11 +3096,11 @@
       <c r="C69" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="23"/>
+      <c r="D69" s="22"/>
       <c r="E69" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F69" s="20" t="s">
+      <c r="F69" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -3188,11 +3117,11 @@
       <c r="C70" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="23"/>
+      <c r="D70" s="22"/>
       <c r="E70" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="19" t="s">
         <v>288</v>
       </c>
       <c r="G70" s="2" t="s">
@@ -3209,11 +3138,11 @@
       <c r="C71" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D71" s="23"/>
+      <c r="D71" s="22"/>
       <c r="E71" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F71" s="20" t="s">
+      <c r="F71" s="19" t="s">
         <v>316</v>
       </c>
       <c r="G71" s="2" t="s">
@@ -3230,11 +3159,11 @@
       <c r="C72" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="23"/>
+      <c r="D72" s="22"/>
       <c r="E72" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F72" s="20" t="s">
+      <c r="F72" s="19" t="s">
         <v>119</v>
       </c>
       <c r="G72" s="5" t="s">
@@ -3251,11 +3180,11 @@
       <c r="C73" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D73" s="23"/>
+      <c r="D73" s="22"/>
       <c r="E73" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="F73" s="19" t="s">
         <v>351</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -3272,11 +3201,11 @@
       <c r="C74" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D74" s="23"/>
+      <c r="D74" s="22"/>
       <c r="E74" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="F74" s="19" t="s">
         <v>246</v>
       </c>
       <c r="G74" s="2" t="s">
@@ -3293,11 +3222,11 @@
       <c r="C75" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D75" s="23"/>
+      <c r="D75" s="22"/>
       <c r="E75" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="F75" s="19" t="s">
         <v>354</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -3314,11 +3243,11 @@
       <c r="C76" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="20">
+      <c r="F76" s="19">
         <v>28401102104641</v>
       </c>
       <c r="G76" s="10"/>
@@ -3333,11 +3262,11 @@
       <c r="C77" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D77" s="23"/>
+      <c r="D77" s="22"/>
       <c r="E77" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F77" s="20" t="s">
+      <c r="F77" s="19" t="s">
         <v>88</v>
       </c>
       <c r="G77" s="2" t="s">
@@ -3354,11 +3283,11 @@
       <c r="C78" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D78" s="23"/>
+      <c r="D78" s="22"/>
       <c r="E78" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F78" s="20" t="s">
+      <c r="F78" s="19" t="s">
         <v>169</v>
       </c>
       <c r="G78" s="7" t="s">
@@ -3375,11 +3304,11 @@
       <c r="C79" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D79" s="23"/>
+      <c r="D79" s="22"/>
       <c r="E79" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="F79" s="20" t="s">
+      <c r="F79" s="19" t="s">
         <v>320</v>
       </c>
       <c r="G79" s="2" t="s">
@@ -3396,11 +3325,11 @@
       <c r="C80" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D80" s="23"/>
+      <c r="D80" s="22"/>
       <c r="E80" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="F80" s="19" t="s">
         <v>172</v>
       </c>
       <c r="G80" s="7" t="s">
@@ -3417,11 +3346,11 @@
       <c r="C81" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="20">
+      <c r="F81" s="19">
         <v>27201012102167</v>
       </c>
       <c r="G81" s="10"/>
@@ -3436,11 +3365,11 @@
       <c r="C82" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D82" s="23"/>
+      <c r="D82" s="22"/>
       <c r="E82" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="F82" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G82" s="2" t="s">
@@ -3457,11 +3386,11 @@
       <c r="C83" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D83" s="23" t="s">
+      <c r="D83" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="20">
+      <c r="F83" s="19">
         <v>28110261702091</v>
       </c>
       <c r="G83" s="10"/>
@@ -3476,11 +3405,11 @@
       <c r="C84" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="23"/>
+      <c r="D84" s="22"/>
       <c r="E84" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F84" s="20" t="s">
+      <c r="F84" s="19" t="s">
         <v>142</v>
       </c>
       <c r="G84" s="2" t="s">
@@ -3497,11 +3426,11 @@
       <c r="C85" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D85" s="23"/>
+      <c r="D85" s="22"/>
       <c r="E85" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F85" s="20" t="s">
+      <c r="F85" s="19" t="s">
         <v>357</v>
       </c>
       <c r="G85" s="2" t="s">
@@ -3518,11 +3447,11 @@
       <c r="C86" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D86" s="23"/>
+      <c r="D86" s="22"/>
       <c r="E86" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F86" s="20" t="s">
+      <c r="F86" s="19" t="s">
         <v>47</v>
       </c>
       <c r="G86" s="2" t="s">
@@ -3539,11 +3468,11 @@
       <c r="C87" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D87" s="23" t="s">
+      <c r="D87" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E87" s="5"/>
-      <c r="F87" s="20">
+      <c r="F87" s="19">
         <v>27808152102606</v>
       </c>
       <c r="G87" s="10"/>
@@ -3558,11 +3487,11 @@
       <c r="C88" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D88" s="23"/>
+      <c r="D88" s="22"/>
       <c r="E88" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F88" s="20" t="s">
+      <c r="F88" s="19" t="s">
         <v>218</v>
       </c>
       <c r="G88" s="7" t="s">
@@ -3579,11 +3508,11 @@
       <c r="C89" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D89" s="23"/>
+      <c r="D89" s="22"/>
       <c r="E89" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F89" s="20" t="s">
+      <c r="F89" s="19" t="s">
         <v>175</v>
       </c>
       <c r="G89" s="7" t="s">
@@ -3600,11 +3529,11 @@
       <c r="C90" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D90" s="23"/>
+      <c r="D90" s="22"/>
       <c r="E90" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F90" s="20" t="s">
+      <c r="F90" s="19" t="s">
         <v>68</v>
       </c>
       <c r="G90" s="2" t="s">
@@ -3621,11 +3550,11 @@
       <c r="C91" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E91" s="5"/>
-      <c r="F91" s="20">
+      <c r="F91" s="19">
         <v>28909032100795</v>
       </c>
       <c r="G91" s="10"/>
@@ -3640,11 +3569,11 @@
       <c r="C92" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D92" s="23"/>
+      <c r="D92" s="22"/>
       <c r="E92" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="F92" s="20" t="s">
+      <c r="F92" s="19" t="s">
         <v>271</v>
       </c>
       <c r="G92" s="2" t="s">
@@ -3661,11 +3590,11 @@
       <c r="C93" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E93" s="5"/>
-      <c r="F93" s="20">
+      <c r="F93" s="19">
         <v>28006052302114</v>
       </c>
       <c r="G93" s="10"/>
@@ -3680,11 +3609,11 @@
       <c r="C94" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D94" s="23"/>
+      <c r="D94" s="22"/>
       <c r="E94" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F94" s="20" t="s">
+      <c r="F94" s="19" t="s">
         <v>236</v>
       </c>
       <c r="G94" s="2" t="s">
@@ -3699,11 +3628,11 @@
       <c r="C95" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="22" t="s">
         <v>381</v>
       </c>
       <c r="E95" s="5"/>
-      <c r="F95" s="20">
+      <c r="F95" s="19">
         <v>27407200104921</v>
       </c>
       <c r="G95" s="10"/>
@@ -3718,11 +3647,11 @@
       <c r="C96" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D96" s="23"/>
+      <c r="D96" s="22"/>
       <c r="E96" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F96" s="20" t="s">
+      <c r="F96" s="19" t="s">
         <v>178</v>
       </c>
       <c r="G96" s="7" t="s">
@@ -3739,11 +3668,11 @@
       <c r="C97" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D97" s="23" t="s">
+      <c r="D97" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E97" s="5"/>
-      <c r="F97" s="20">
+      <c r="F97" s="19">
         <v>28408182100166</v>
       </c>
       <c r="G97" s="10"/>
@@ -3758,11 +3687,11 @@
       <c r="C98" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D98" s="23"/>
+      <c r="D98" s="22"/>
       <c r="E98" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F98" s="20" t="s">
+      <c r="F98" s="19" t="s">
         <v>91</v>
       </c>
       <c r="G98" s="2" t="s">
@@ -3779,11 +3708,11 @@
       <c r="C99" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D99" s="23" t="s">
+      <c r="D99" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E99" s="5"/>
-      <c r="F99" s="20">
+      <c r="F99" s="19">
         <v>28503242100066</v>
       </c>
       <c r="G99" s="10"/>
@@ -3798,11 +3727,11 @@
       <c r="C100" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D100" s="23"/>
+      <c r="D100" s="22"/>
       <c r="E100" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F100" s="20" t="s">
+      <c r="F100" s="19" t="s">
         <v>181</v>
       </c>
       <c r="G100" s="7" t="s">
@@ -3819,11 +3748,11 @@
       <c r="C101" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D101" s="23"/>
+      <c r="D101" s="22"/>
       <c r="E101" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F101" s="20" t="s">
+      <c r="F101" s="19" t="s">
         <v>194</v>
       </c>
       <c r="G101" s="7" t="s">
@@ -3840,11 +3769,11 @@
       <c r="C102" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D102" s="23"/>
+      <c r="D102" s="22"/>
       <c r="E102" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F102" s="20" t="s">
+      <c r="F102" s="19" t="s">
         <v>184</v>
       </c>
       <c r="G102" s="7" t="s">
@@ -3861,11 +3790,11 @@
       <c r="C103" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D103" s="23"/>
+      <c r="D103" s="22"/>
       <c r="E103" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F103" s="20" t="s">
+      <c r="F103" s="19" t="s">
         <v>187</v>
       </c>
       <c r="G103" s="7" t="s">
@@ -3882,11 +3811,11 @@
       <c r="C104" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D104" s="23" t="s">
+      <c r="D104" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E104" s="5"/>
-      <c r="F104" s="20">
+      <c r="F104" s="19">
         <v>27508062100457</v>
       </c>
       <c r="G104" s="10"/>
@@ -3901,11 +3830,11 @@
       <c r="C105" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D105" s="23"/>
+      <c r="D105" s="22"/>
       <c r="E105" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F105" s="20" t="s">
+      <c r="F105" s="19" t="s">
         <v>71</v>
       </c>
       <c r="G105" s="2" t="s">
@@ -3920,11 +3849,11 @@
       <c r="C106" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="22" t="s">
         <v>381</v>
       </c>
       <c r="E106" s="5"/>
-      <c r="F106" s="20">
+      <c r="F106" s="19">
         <v>27012292100256</v>
       </c>
       <c r="G106" s="10"/>
@@ -3939,11 +3868,11 @@
       <c r="C107" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D107" s="23"/>
+      <c r="D107" s="22"/>
       <c r="E107" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F107" s="20" t="s">
+      <c r="F107" s="19" t="s">
         <v>331</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -3960,11 +3889,11 @@
       <c r="C108" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D108" s="23"/>
+      <c r="D108" s="22"/>
       <c r="E108" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F108" s="20" t="s">
+      <c r="F108" s="19" t="s">
         <v>190</v>
       </c>
       <c r="G108" s="7" t="s">
@@ -3981,11 +3910,11 @@
       <c r="C109" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D109" s="23"/>
+      <c r="D109" s="22"/>
       <c r="E109" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F109" s="20" t="s">
+      <c r="F109" s="19" t="s">
         <v>239</v>
       </c>
       <c r="G109" s="2" t="s">
@@ -4002,11 +3931,11 @@
       <c r="C110" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D110" s="23"/>
+      <c r="D110" s="22"/>
       <c r="E110" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F110" s="20" t="s">
+      <c r="F110" s="19" t="s">
         <v>324</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -4023,11 +3952,11 @@
       <c r="C111" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D111" s="23"/>
+      <c r="D111" s="22"/>
       <c r="E111" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F111" s="20" t="s">
+      <c r="F111" s="19" t="s">
         <v>145</v>
       </c>
       <c r="G111" s="2" t="s">
@@ -4044,11 +3973,11 @@
       <c r="C112" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="23"/>
+      <c r="D112" s="22"/>
       <c r="E112" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F112" s="20" t="s">
+      <c r="F112" s="19" t="s">
         <v>122</v>
       </c>
       <c r="G112" s="12" t="s">
@@ -4065,11 +3994,11 @@
       <c r="C113" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D113" s="23" t="s">
+      <c r="D113" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E113" s="5"/>
-      <c r="F113" s="20">
+      <c r="F113" s="19">
         <v>27810032103387</v>
       </c>
     </row>
@@ -4083,11 +4012,11 @@
       <c r="C114" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D114" s="23"/>
+      <c r="D114" s="22"/>
       <c r="E114" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="F114" s="20" t="s">
+      <c r="F114" s="19" t="s">
         <v>328</v>
       </c>
       <c r="G114" s="11" t="s">
@@ -4104,11 +4033,11 @@
       <c r="C115" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="D115" s="23" t="s">
+      <c r="D115" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E115" s="5"/>
-      <c r="F115" s="20">
+      <c r="F115" s="19">
         <v>27606222101376</v>
       </c>
     </row>
@@ -4122,11 +4051,11 @@
       <c r="C116" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D116" s="23"/>
+      <c r="D116" s="22"/>
       <c r="E116" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F116" s="20" t="s">
+      <c r="F116" s="19" t="s">
         <v>363</v>
       </c>
       <c r="G116" s="11" t="s">
@@ -4143,11 +4072,11 @@
       <c r="C117" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="D117" s="23" t="s">
+      <c r="D117" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E117" s="5"/>
-      <c r="F117" s="20">
+      <c r="F117" s="19">
         <v>28707172101366</v>
       </c>
     </row>
@@ -4161,11 +4090,11 @@
       <c r="C118" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D118" s="23"/>
+      <c r="D118" s="22"/>
       <c r="E118" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F118" s="20" t="s">
+      <c r="F118" s="19" t="s">
         <v>200</v>
       </c>
       <c r="G118" s="13" t="s">
@@ -4182,11 +4111,11 @@
       <c r="C119" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D119" s="23"/>
+      <c r="D119" s="22"/>
       <c r="E119" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F119" s="20" t="s">
+      <c r="F119" s="19" t="s">
         <v>203</v>
       </c>
       <c r="G119" s="13" t="s">
@@ -4203,11 +4132,11 @@
       <c r="C120" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D120" s="23"/>
+      <c r="D120" s="22"/>
       <c r="E120" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F120" s="20" t="s">
+      <c r="F120" s="19" t="s">
         <v>125</v>
       </c>
       <c r="G120" s="11" t="s">
@@ -4224,11 +4153,11 @@
       <c r="C121" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D121" s="23"/>
+      <c r="D121" s="22"/>
       <c r="E121" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F121" s="20" t="s">
+      <c r="F121" s="19" t="s">
         <v>197</v>
       </c>
       <c r="G121" s="13" t="s">
@@ -4245,11 +4174,11 @@
       <c r="C122" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D122" s="23"/>
+      <c r="D122" s="22"/>
       <c r="E122" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F122" s="20" t="s">
+      <c r="F122" s="19" t="s">
         <v>128</v>
       </c>
       <c r="G122" s="11" t="s">
@@ -4266,11 +4195,11 @@
       <c r="C123" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D123" s="23"/>
+      <c r="D123" s="22"/>
       <c r="E123" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F123" s="20" t="s">
+      <c r="F123" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G123" s="11" t="s">
@@ -4287,11 +4216,11 @@
       <c r="C124" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D124" s="23"/>
+      <c r="D124" s="22"/>
       <c r="E124" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F124" s="20" t="s">
+      <c r="F124" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G124" s="11" t="s">
@@ -4308,11 +4237,11 @@
       <c r="C125" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D125" s="23"/>
+      <c r="D125" s="22"/>
       <c r="E125" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F125" s="20" t="s">
+      <c r="F125" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G125" s="11" t="s">
@@ -4329,11 +4258,11 @@
       <c r="C126" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D126" s="23"/>
+      <c r="D126" s="22"/>
       <c r="E126" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F126" s="20" t="s">
+      <c r="F126" s="19" t="s">
         <v>221</v>
       </c>
       <c r="G126" s="13" t="s">
@@ -4350,11 +4279,11 @@
       <c r="C127" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="D127" s="23" t="s">
+      <c r="D127" s="22" t="s">
         <v>382</v>
       </c>
       <c r="E127" s="5"/>
-      <c r="F127" s="20">
+      <c r="F127" s="19">
         <v>26910230100165</v>
       </c>
     </row>
@@ -4368,11 +4297,11 @@
       <c r="C128" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D128" s="23"/>
+      <c r="D128" s="22"/>
       <c r="E128" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F128" s="20" t="s">
+      <c r="F128" s="19" t="s">
         <v>148</v>
       </c>
       <c r="G128" s="11" t="s">
@@ -4389,11 +4318,11 @@
       <c r="C129" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D129" s="23"/>
+      <c r="D129" s="22"/>
       <c r="E129" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="20" t="s">
+      <c r="F129" s="19" t="s">
         <v>22</v>
       </c>
       <c r="G129" s="11" t="s">
@@ -4410,11 +4339,11 @@
       <c r="C130" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D130" s="23"/>
+      <c r="D130" s="22"/>
       <c r="E130" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F130" s="20" t="s">
+      <c r="F130" s="19" t="s">
         <v>131</v>
       </c>
       <c r="G130" s="11" t="s">
@@ -4431,11 +4360,11 @@
       <c r="C131" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D131" s="23"/>
+      <c r="D131" s="22"/>
       <c r="E131" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F131" s="20" t="s">
+      <c r="F131" s="19" t="s">
         <v>51</v>
       </c>
       <c r="G131" s="11" t="s">
@@ -4452,11 +4381,11 @@
       <c r="C132" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D132" s="23"/>
+      <c r="D132" s="22"/>
       <c r="E132" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F132" s="20" t="s">
+      <c r="F132" s="19" t="s">
         <v>134</v>
       </c>
       <c r="G132" s="11" t="s">
@@ -4473,11 +4402,11 @@
       <c r="C133" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D133" s="23"/>
+      <c r="D133" s="22"/>
       <c r="E133" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F133" s="20" t="s">
+      <c r="F133" s="19" t="s">
         <v>366</v>
       </c>
       <c r="G133" s="11" t="s">
@@ -4494,11 +4423,11 @@
       <c r="C134" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D134" s="23"/>
+      <c r="D134" s="22"/>
       <c r="E134" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F134" s="20" t="s">
+      <c r="F134" s="19" t="s">
         <v>369</v>
       </c>
       <c r="G134" s="11" t="s">
@@ -4515,11 +4444,11 @@
       <c r="C135" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D135" s="23"/>
+      <c r="D135" s="22"/>
       <c r="E135" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F135" s="20" t="s">
+      <c r="F135" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G135" s="11" t="s">
@@ -4536,11 +4465,11 @@
       <c r="C136" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D136" s="23"/>
+      <c r="D136" s="22"/>
       <c r="E136" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F136" s="20" t="s">
+      <c r="F136" s="19" t="s">
         <v>206</v>
       </c>
       <c r="G136" s="13" t="s">
@@ -4560,10 +4489,10 @@
       <c r="D137" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="E137" s="17" t="s">
+      <c r="E137" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="F137" s="20" t="s">
+      <c r="F137" s="19" t="s">
         <v>372</v>
       </c>
       <c r="G137" s="11" t="s">
@@ -4580,9 +4509,9 @@
       <c r="C138" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="D138" s="25"/>
-      <c r="E138" s="17"/>
-      <c r="F138" s="20">
+      <c r="D138" s="26"/>
+      <c r="E138" s="25"/>
+      <c r="F138" s="19">
         <v>27807230100481</v>
       </c>
     </row>
@@ -4596,11 +4525,11 @@
       <c r="C139" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D139" s="23"/>
+      <c r="D139" s="22"/>
       <c r="E139" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F139" s="20" t="s">
+      <c r="F139" s="19" t="s">
         <v>242</v>
       </c>
       <c r="G139" s="11" t="s">
@@ -4617,11 +4546,11 @@
       <c r="C140" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D140" s="23"/>
+      <c r="D140" s="22"/>
       <c r="E140" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F140" s="20" t="s">
+      <c r="F140" s="19" t="s">
         <v>74</v>
       </c>
       <c r="G140" s="11" t="s">
@@ -4638,11 +4567,11 @@
       <c r="C141" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D141" s="23"/>
+      <c r="D141" s="22"/>
       <c r="E141" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F141" s="20" t="s">
+      <c r="F141" s="19" t="s">
         <v>250</v>
       </c>
       <c r="G141" s="11" t="s">
@@ -4659,11 +4588,11 @@
       <c r="C142" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D142" s="23"/>
+      <c r="D142" s="22"/>
       <c r="E142" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F142" s="20" t="s">
+      <c r="F142" s="19" t="s">
         <v>291</v>
       </c>
       <c r="G142" s="11" t="s">
@@ -4680,11 +4609,11 @@
       <c r="C143" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D143" s="23"/>
+      <c r="D143" s="22"/>
       <c r="E143" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F143" s="20" t="s">
+      <c r="F143" s="19" t="s">
         <v>294</v>
       </c>
       <c r="G143" s="11" t="s">
@@ -4695,9 +4624,8 @@
   <sortState ref="A2:F143">
     <sortCondition ref="C1"/>
   </sortState>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="E137:E138"/>
-    <mergeCell ref="D137:D138"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
